--- a/datos/indicadores_adelantados/cemento/ventas_cemento_depto_1991_2026.xlsx
+++ b/datos/indicadores_adelantados/cemento/ventas_cemento_depto_1991_2026.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\3. IGAE\2026-08 Agosto\5. Cemento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\1. Página Web\2026 - 09. Septiembre\Cemento 6-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDB82F3-8658-418A-B60E-10E8090D87AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10605" windowHeight="11010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1000" calcOnSave="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="26">
   <si>
     <t>PERIODO</t>
   </si>
@@ -172,12 +173,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="#,##0_ ;\-#,##0\ "/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -417,11 +417,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -488,29 +489,27 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 7" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -645,6 +644,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -680,6 +696,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -855,7 +888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG508"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -15157,7 +15190,7 @@
       <c r="O467" s="3"/>
       <c r="P467" s="3"/>
     </row>
-    <row r="468" spans="2:16" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="468" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B468" s="15">
         <v>2024</v>
       </c>
@@ -15176,7 +15209,7 @@
       <c r="G468" s="21">
         <v>258524.41999999998</v>
       </c>
-      <c r="H468" s="29">
+      <c r="H468" s="28">
         <v>1053147.0159500015</v>
       </c>
       <c r="I468" s="21">
@@ -15209,7 +15242,7 @@
       <c r="G469" s="20">
         <v>19494.300000000003</v>
       </c>
-      <c r="H469" s="30">
+      <c r="H469" s="29">
         <v>99071.219999999797</v>
       </c>
       <c r="I469" s="20">
@@ -15242,7 +15275,7 @@
       <c r="G470" s="20">
         <v>26581.329999999998</v>
       </c>
-      <c r="H470" s="30">
+      <c r="H470" s="29">
         <v>69738.929999999556</v>
       </c>
       <c r="I470" s="20">
@@ -15275,7 +15308,7 @@
       <c r="G471" s="20">
         <v>13727.439999999999</v>
       </c>
-      <c r="H471" s="31">
+      <c r="H471" s="30">
         <v>78610.679999999455</v>
       </c>
       <c r="I471" s="20">
@@ -15308,7 +15341,7 @@
       <c r="G472" s="20">
         <v>19730.099999999999</v>
       </c>
-      <c r="H472" s="31">
+      <c r="H472" s="30">
         <v>82941.330000000249</v>
       </c>
       <c r="I472" s="20">
@@ -15341,7 +15374,7 @@
       <c r="G473" s="20">
         <v>17259.61</v>
       </c>
-      <c r="H473" s="31">
+      <c r="H473" s="30">
         <v>85540.270000000062</v>
       </c>
       <c r="I473" s="20">
@@ -15374,7 +15407,7 @@
       <c r="G474" s="20">
         <v>17687.330000000002</v>
       </c>
-      <c r="H474" s="31">
+      <c r="H474" s="30">
         <v>90002.610000000059</v>
       </c>
       <c r="I474" s="20">
@@ -15407,7 +15440,7 @@
       <c r="G475" s="20">
         <v>20019.14</v>
       </c>
-      <c r="H475" s="31">
+      <c r="H475" s="30">
         <v>91256.230000000069</v>
       </c>
       <c r="I475" s="20">
@@ -15440,7 +15473,7 @@
       <c r="G476" s="20">
         <v>23344.039999999997</v>
       </c>
-      <c r="H476" s="31">
+      <c r="H476" s="30">
         <v>96770.105950000754</v>
       </c>
       <c r="I476" s="20">
@@ -15473,7 +15506,7 @@
       <c r="G477" s="20">
         <v>21790.519999999997</v>
       </c>
-      <c r="H477" s="31">
+      <c r="H477" s="30">
         <v>99050.740000000762</v>
       </c>
       <c r="I477" s="20">
@@ -15506,7 +15539,7 @@
       <c r="G478" s="20">
         <v>28025.85</v>
       </c>
-      <c r="H478" s="31">
+      <c r="H478" s="30">
         <v>88553.55</v>
       </c>
       <c r="I478" s="20">
@@ -15539,7 +15572,7 @@
       <c r="G479" s="20">
         <v>22319.78</v>
       </c>
-      <c r="H479" s="31">
+      <c r="H479" s="30">
         <v>84343.09000000036</v>
       </c>
       <c r="I479" s="20">
@@ -15572,7 +15605,7 @@
       <c r="G480" s="20">
         <v>28544.979999999996</v>
       </c>
-      <c r="H480" s="31">
+      <c r="H480" s="30">
         <v>87268.260000000359</v>
       </c>
       <c r="I480" s="20">
@@ -15593,7 +15626,7 @@
       <c r="E481" s="20"/>
       <c r="F481" s="20"/>
       <c r="G481" s="20"/>
-      <c r="H481" s="31"/>
+      <c r="H481" s="30"/>
       <c r="I481" s="20"/>
       <c r="J481" s="23"/>
       <c r="K481" s="3"/>
@@ -15603,7 +15636,7 @@
       <c r="O481" s="3"/>
       <c r="P481" s="3"/>
     </row>
-    <row r="482" spans="2:16" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="482" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B482" s="15">
         <v>2025</v>
       </c>
@@ -15622,7 +15655,7 @@
       <c r="G482" s="21">
         <v>276840.12999999971</v>
       </c>
-      <c r="H482" s="29">
+      <c r="H482" s="28">
         <v>1062179.2699999984</v>
       </c>
       <c r="I482" s="21">
@@ -15655,7 +15688,7 @@
       <c r="G483" s="20">
         <v>15637.94</v>
       </c>
-      <c r="H483" s="30">
+      <c r="H483" s="29">
         <v>83691.060000000274</v>
       </c>
       <c r="I483" s="20">
@@ -15688,7 +15721,7 @@
       <c r="G484" s="20">
         <v>22037.41</v>
       </c>
-      <c r="H484" s="30">
+      <c r="H484" s="29">
         <v>93644.549999999028</v>
       </c>
       <c r="I484" s="20">
@@ -15721,7 +15754,7 @@
       <c r="G485" s="20">
         <v>14484.98</v>
       </c>
-      <c r="H485" s="30">
+      <c r="H485" s="29">
         <v>64027.439999999471</v>
       </c>
       <c r="I485" s="20">
@@ -15754,7 +15787,7 @@
       <c r="G486" s="20">
         <v>16302.65</v>
       </c>
-      <c r="H486" s="30">
+      <c r="H486" s="29">
         <v>81492.919999999547</v>
       </c>
       <c r="I486" s="20">
@@ -15787,7 +15820,7 @@
       <c r="G487" s="20">
         <v>31716.109999999986</v>
       </c>
-      <c r="H487" s="30">
+      <c r="H487" s="29">
         <v>90495.110000000146</v>
       </c>
       <c r="I487" s="20">
@@ -15820,7 +15853,7 @@
       <c r="G488" s="20">
         <v>29530.03</v>
       </c>
-      <c r="H488" s="30">
+      <c r="H488" s="29">
         <v>92038.98000000001</v>
       </c>
       <c r="I488" s="20">
@@ -15853,7 +15886,7 @@
       <c r="G489" s="20">
         <v>27151.97</v>
       </c>
-      <c r="H489" s="30">
+      <c r="H489" s="29">
         <v>117120.80000000002</v>
       </c>
       <c r="I489" s="20">
@@ -15886,7 +15919,7 @@
       <c r="G490" s="20">
         <v>19661.05</v>
       </c>
-      <c r="H490" s="30">
+      <c r="H490" s="29">
         <v>98461.479999999967</v>
       </c>
       <c r="I490" s="20">
@@ -15919,7 +15952,7 @@
       <c r="G491" s="20">
         <v>25715.569999999898</v>
       </c>
-      <c r="H491" s="30">
+      <c r="H491" s="29">
         <v>87374.97</v>
       </c>
       <c r="I491" s="20">
@@ -15952,7 +15985,7 @@
       <c r="G492" s="20">
         <v>32501.97</v>
       </c>
-      <c r="H492" s="30">
+      <c r="H492" s="29">
         <v>75107.5799999999</v>
       </c>
       <c r="I492" s="20">
@@ -15985,7 +16018,7 @@
       <c r="G493" s="20">
         <v>20729.289999999899</v>
       </c>
-      <c r="H493" s="30">
+      <c r="H493" s="29">
         <v>91275.959999999992</v>
       </c>
       <c r="I493" s="20">
@@ -16018,7 +16051,7 @@
       <c r="G494" s="20">
         <v>21371.16</v>
       </c>
-      <c r="H494" s="30">
+      <c r="H494" s="29">
         <v>87448.419999999911</v>
       </c>
       <c r="I494" s="20">
@@ -16039,7 +16072,7 @@
       <c r="E495" s="20"/>
       <c r="F495" s="20"/>
       <c r="G495" s="20"/>
-      <c r="H495" s="30"/>
+      <c r="H495" s="29"/>
       <c r="I495" s="20"/>
       <c r="J495" s="23"/>
       <c r="K495" s="3"/>
@@ -16054,25 +16087,32 @@
         <v>24</v>
       </c>
       <c r="C496" s="21">
-        <v>314822.24</v>
+        <f>SUM(C497:C503)</f>
+        <v>399830.31499999994</v>
       </c>
       <c r="D496" s="21">
-        <v>193122.90799999988</v>
+        <f t="shared" ref="D496:H496" si="0">SUM(D497:D503)</f>
+        <v>251128.90799999988</v>
       </c>
       <c r="E496" s="21">
-        <v>186518.26</v>
+        <f t="shared" si="0"/>
+        <v>249949.97</v>
       </c>
       <c r="F496" s="21">
-        <v>163371.61999999991</v>
+        <f t="shared" si="0"/>
+        <v>179370.11999999991</v>
       </c>
       <c r="G496" s="21">
-        <v>92915.019999999873</v>
+        <f t="shared" si="0"/>
+        <v>119935.01999999987</v>
       </c>
       <c r="H496" s="21">
-        <v>454048.03899999987</v>
+        <f t="shared" si="0"/>
+        <v>558912.62999999989</v>
       </c>
       <c r="I496" s="21">
-        <v>1404798.0869999996</v>
+        <f>SUM(C496:H496)</f>
+        <v>1759126.9629999993</v>
       </c>
       <c r="J496" s="23"/>
       <c r="K496" s="3"/>
@@ -16101,10 +16141,11 @@
       <c r="G497" s="20">
         <v>16082.5</v>
       </c>
-      <c r="H497" s="30">
+      <c r="H497" s="29">
         <v>96316.08</v>
       </c>
       <c r="I497" s="20">
+        <f>SUM(C497:H497)</f>
         <v>255767.8279999998</v>
       </c>
       <c r="J497" s="23"/>
@@ -16134,10 +16175,11 @@
       <c r="G498" s="20">
         <v>16592.66</v>
       </c>
-      <c r="H498" s="30">
+      <c r="H498" s="29">
         <v>65909.01999999999</v>
       </c>
       <c r="I498" s="20">
+        <f t="shared" ref="I498:I502" si="1">SUM(C498:H498)</f>
         <v>201091.49000000002</v>
       </c>
       <c r="J498" s="23"/>
@@ -16167,10 +16209,11 @@
       <c r="G499" s="20">
         <v>18805.320000000003</v>
       </c>
-      <c r="H499" s="30">
+      <c r="H499" s="29">
         <v>79435.429999999993</v>
       </c>
       <c r="I499" s="20">
+        <f t="shared" si="1"/>
         <v>255710.32</v>
       </c>
       <c r="J499" s="23"/>
@@ -16200,10 +16243,11 @@
       <c r="G500" s="20">
         <v>12828.399999999991</v>
       </c>
-      <c r="H500" s="30">
+      <c r="H500" s="29">
         <v>77210.999999999898</v>
       </c>
       <c r="I500" s="20">
+        <f t="shared" si="1"/>
         <v>258374.00999999989</v>
       </c>
       <c r="J500" s="23"/>
@@ -16233,10 +16277,11 @@
       <c r="G501" s="20">
         <v>12454.55999999999</v>
       </c>
-      <c r="H501" s="30">
+      <c r="H501" s="29">
         <v>74749.570000000007</v>
       </c>
       <c r="I501" s="20">
+        <f t="shared" si="1"/>
         <v>210703.83000000002</v>
       </c>
       <c r="J501" s="23"/>
@@ -16266,11 +16311,12 @@
       <c r="G502" s="20">
         <v>16151.5799999999</v>
       </c>
-      <c r="H502" s="30">
-        <v>60426.938999999998</v>
+      <c r="H502" s="29">
+        <v>81922.52</v>
       </c>
       <c r="I502" s="20">
-        <v>223150.60899999988</v>
+        <f t="shared" si="1"/>
+        <v>244646.18999999989</v>
       </c>
       <c r="J502" s="23"/>
       <c r="K502" s="3"/>
@@ -16281,14 +16327,31 @@
       <c r="P502" s="3"/>
     </row>
     <row r="503" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B503" s="19"/>
-      <c r="C503" s="22"/>
-      <c r="D503" s="22"/>
-      <c r="E503" s="22"/>
-      <c r="F503" s="22"/>
-      <c r="G503" s="22"/>
-      <c r="H503" s="34"/>
-      <c r="I503" s="22"/>
+      <c r="B503" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C503" s="20">
+        <v>85008.074999999983</v>
+      </c>
+      <c r="D503" s="20">
+        <v>58006</v>
+      </c>
+      <c r="E503" s="20">
+        <v>63431.71</v>
+      </c>
+      <c r="F503" s="20">
+        <v>15998.5</v>
+      </c>
+      <c r="G503" s="20">
+        <v>27020</v>
+      </c>
+      <c r="H503" s="29">
+        <v>83369.010000000009</v>
+      </c>
+      <c r="I503" s="20">
+        <f t="shared" ref="I503" si="2">SUM(C503:H503)</f>
+        <v>332833.29499999998</v>
+      </c>
       <c r="J503" s="23"/>
       <c r="K503" s="3"/>
       <c r="L503" s="3"/>
@@ -16298,16 +16361,14 @@
       <c r="P503" s="3"/>
     </row>
     <row r="504" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B504" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C504" s="32"/>
-      <c r="D504" s="32"/>
-      <c r="E504" s="32"/>
-      <c r="F504" s="32"/>
-      <c r="G504" s="32"/>
-      <c r="H504" s="32"/>
-      <c r="I504" s="32"/>
+      <c r="B504" s="19"/>
+      <c r="C504" s="22"/>
+      <c r="D504" s="22"/>
+      <c r="E504" s="22"/>
+      <c r="F504" s="22"/>
+      <c r="G504" s="22"/>
+      <c r="H504" s="33"/>
+      <c r="I504" s="22"/>
       <c r="J504" s="23"/>
       <c r="K504" s="3"/>
       <c r="L504" s="3"/>
@@ -16316,29 +16377,39 @@
       <c r="O504" s="3"/>
       <c r="P504" s="3"/>
     </row>
-    <row r="505" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B505" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="H505" s="4"/>
+    <row r="505" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B505" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C505" s="31"/>
+      <c r="D505" s="31"/>
+      <c r="E505" s="31"/>
+      <c r="F505" s="31"/>
+      <c r="G505" s="31"/>
+      <c r="H505" s="31"/>
+      <c r="I505" s="31"/>
+      <c r="J505" s="23"/>
+      <c r="K505" s="3"/>
+      <c r="L505" s="3"/>
+      <c r="M505" s="3"/>
+      <c r="N505" s="3"/>
+      <c r="O505" s="3"/>
+      <c r="P505" s="3"/>
     </row>
     <row r="506" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B506" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H506" s="4"/>
+    </row>
+    <row r="507" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B507" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="H506" s="4"/>
-    </row>
-    <row r="507" spans="2:16" x14ac:dyDescent="0.2">
       <c r="H507" s="4"/>
     </row>
     <row r="508" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="C508" s="28"/>
-      <c r="D508" s="28"/>
-      <c r="E508" s="28"/>
-      <c r="F508" s="28"/>
-      <c r="G508" s="28"/>
-      <c r="H508" s="28"/>
-      <c r="I508" s="28"/>
+      <c r="H508" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datos/indicadores_adelantados/cemento/ventas_cemento_depto_1991_2026.xlsx
+++ b/datos/indicadores_adelantados/cemento/ventas_cemento_depto_1991_2026.xlsx
@@ -5,18 +5,27 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\1. Página Web\2026 - 09. Septiembre\Cemento 6-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\1. Página Web\2026 - 10 Octubre\Cemento 8-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDB82F3-8658-418A-B60E-10E8090D87AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53B68DC-BD10-4A12-BEF1-01B119BD1CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateCount="1000" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="26">
   <si>
     <t>PERIODO</t>
   </si>
@@ -179,7 +188,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,6 +288,19 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF002060"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF002060"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -422,7 +444,7 @@
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -504,6 +526,15 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -889,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG508"/>
+  <dimension ref="A1:AG509"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="2" customWidth="1"/>
@@ -16087,32 +16118,32 @@
         <v>24</v>
       </c>
       <c r="C496" s="21">
-        <f>SUM(C497:C503)</f>
-        <v>399830.31499999994</v>
+        <f>SUM(C497:C504)</f>
+        <v>477114.21499999997</v>
       </c>
       <c r="D496" s="21">
-        <f t="shared" ref="D496:H496" si="0">SUM(D497:D503)</f>
-        <v>251128.90799999988</v>
+        <f t="shared" ref="D496:I496" si="0">SUM(D497:D504)</f>
+        <v>267306.31799999985</v>
       </c>
       <c r="E496" s="21">
         <f t="shared" si="0"/>
-        <v>249949.97</v>
+        <v>320451.54000000004</v>
       </c>
       <c r="F496" s="21">
         <f t="shared" si="0"/>
-        <v>179370.11999999991</v>
+        <v>203132.63999999981</v>
       </c>
       <c r="G496" s="21">
         <f t="shared" si="0"/>
-        <v>119935.01999999987</v>
+        <v>175257.26999999987</v>
       </c>
       <c r="H496" s="21">
         <f t="shared" si="0"/>
-        <v>558912.62999999989</v>
+        <v>618768.17999999993</v>
       </c>
       <c r="I496" s="21">
-        <f>SUM(C496:H496)</f>
-        <v>1759126.9629999993</v>
+        <f t="shared" si="0"/>
+        <v>2062030.1629999995</v>
       </c>
       <c r="J496" s="23"/>
       <c r="K496" s="3"/>
@@ -16122,7 +16153,7 @@
       <c r="O496" s="3"/>
       <c r="P496" s="3"/>
     </row>
-    <row r="497" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="497" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B497" s="17" t="s">
         <v>1</v>
       </c>
@@ -16156,7 +16187,7 @@
       <c r="O497" s="3"/>
       <c r="P497" s="3"/>
     </row>
-    <row r="498" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="498" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B498" s="17" t="s">
         <v>2</v>
       </c>
@@ -16190,7 +16221,7 @@
       <c r="O498" s="3"/>
       <c r="P498" s="3"/>
     </row>
-    <row r="499" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="499" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B499" s="17" t="s">
         <v>3</v>
       </c>
@@ -16224,7 +16255,7 @@
       <c r="O499" s="3"/>
       <c r="P499" s="3"/>
     </row>
-    <row r="500" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="500" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B500" s="17" t="s">
         <v>4</v>
       </c>
@@ -16258,7 +16289,7 @@
       <c r="O500" s="3"/>
       <c r="P500" s="3"/>
     </row>
-    <row r="501" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="501" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B501" s="17" t="s">
         <v>5</v>
       </c>
@@ -16292,7 +16323,7 @@
       <c r="O501" s="3"/>
       <c r="P501" s="3"/>
     </row>
-    <row r="502" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="502" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B502" s="17" t="s">
         <v>6</v>
       </c>
@@ -16326,29 +16357,29 @@
       <c r="O502" s="3"/>
       <c r="P502" s="3"/>
     </row>
-    <row r="503" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="503" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B503" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C503" s="20">
+      <c r="C503" s="35">
         <v>85008.074999999983</v>
       </c>
-      <c r="D503" s="20">
+      <c r="D503" s="35">
         <v>58006</v>
       </c>
-      <c r="E503" s="20">
+      <c r="E503" s="35">
         <v>63431.71</v>
       </c>
-      <c r="F503" s="20">
+      <c r="F503" s="35">
         <v>15998.5</v>
       </c>
-      <c r="G503" s="20">
+      <c r="G503" s="35">
         <v>27020</v>
       </c>
       <c r="H503" s="29">
         <v>83369.010000000009</v>
       </c>
-      <c r="I503" s="20">
+      <c r="I503" s="36">
         <f t="shared" ref="I503" si="2">SUM(C503:H503)</f>
         <v>332833.29499999998</v>
       </c>
@@ -16360,15 +16391,31 @@
       <c r="O503" s="3"/>
       <c r="P503" s="3"/>
     </row>
-    <row r="504" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B504" s="19"/>
-      <c r="C504" s="22"/>
-      <c r="D504" s="22"/>
-      <c r="E504" s="22"/>
-      <c r="F504" s="22"/>
-      <c r="G504" s="22"/>
-      <c r="H504" s="33"/>
-      <c r="I504" s="22"/>
+    <row r="504" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B504" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C504" s="35">
+        <v>77283.900000000009</v>
+      </c>
+      <c r="D504" s="35">
+        <v>16177.41</v>
+      </c>
+      <c r="E504" s="35">
+        <v>70501.570000000007</v>
+      </c>
+      <c r="F504" s="35">
+        <v>23762.519999999899</v>
+      </c>
+      <c r="G504" s="35">
+        <v>55322.25</v>
+      </c>
+      <c r="H504" s="29">
+        <v>59855.55</v>
+      </c>
+      <c r="I504" s="36">
+        <v>302903.1999999999</v>
+      </c>
       <c r="J504" s="23"/>
       <c r="K504" s="3"/>
       <c r="L504" s="3"/>
@@ -16377,17 +16424,15 @@
       <c r="O504" s="3"/>
       <c r="P504" s="3"/>
     </row>
-    <row r="505" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B505" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C505" s="31"/>
-      <c r="D505" s="31"/>
-      <c r="E505" s="31"/>
-      <c r="F505" s="31"/>
-      <c r="G505" s="31"/>
-      <c r="H505" s="31"/>
-      <c r="I505" s="31"/>
+    <row r="505" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B505" s="19"/>
+      <c r="C505" s="22"/>
+      <c r="D505" s="22"/>
+      <c r="E505" s="22"/>
+      <c r="F505" s="22"/>
+      <c r="G505" s="22"/>
+      <c r="H505" s="33"/>
+      <c r="I505" s="22"/>
       <c r="J505" s="23"/>
       <c r="K505" s="3"/>
       <c r="L505" s="3"/>
@@ -16396,20 +16441,41 @@
       <c r="O505" s="3"/>
       <c r="P505" s="3"/>
     </row>
-    <row r="506" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B506" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="H506" s="4"/>
+    <row r="506" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B506" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C506" s="31"/>
+      <c r="D506" s="31"/>
+      <c r="E506" s="31"/>
+      <c r="F506" s="31"/>
+      <c r="G506" s="31"/>
+      <c r="H506" s="31"/>
+      <c r="I506" s="31"/>
+      <c r="J506" s="23"/>
+      <c r="K506" s="3"/>
+      <c r="L506" s="3"/>
+      <c r="M506" s="3"/>
+      <c r="N506" s="3"/>
+      <c r="O506" s="3"/>
+      <c r="P506" s="3"/>
     </row>
     <row r="507" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B507" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H507" s="4"/>
+    </row>
+    <row r="508" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B508" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="H507" s="4"/>
-    </row>
-    <row r="508" spans="2:16" x14ac:dyDescent="0.2">
       <c r="H508" s="4"/>
+    </row>
+    <row r="509" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C509" s="34"/>
+      <c r="D509" s="34"/>
+      <c r="H509" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
